--- a/htr-FHIR/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-composition-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-04T16:07:16+00:00</t>
+    <t>2025-03-06T10:23:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Clinical document utilisé pour représenter un document FHIR.</t>
+    <t>Ce profil est  utilisé pour représenter un document FHIR.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-composition-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T10:23:19+00:00</t>
+    <t>2025-03-10T13:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Ce profil est  utilisé pour représenter un document FHIR.</t>
+    <t>Ce profil est utilisé pour représenter un document médical.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -704,7 +704,7 @@
     <t>Informateur</t>
   </si>
   <si>
-    <t>Extension permettant d'ajouter des informateur dans la Composition.</t>
+    <t>Extension permettant d'ajouter des informateurs dans la Composition.</t>
   </si>
   <si>
     <t>Composition.extension:informationRecipient-extension</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-composition-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-10T13:00:25+00:00</t>
+    <t>2025-03-11T15:29:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-composition-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T15:29:00+00:00</t>
+    <t>2025-03-12T13:18:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-composition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-14T15:47:10+00:00</t>
+    <t>2025-03-25T13:52:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1191,7 +1191,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}comp-3:La valeur du PractitionerRole.code dans l'extension[party]' doit être 'PROV' ou 'AGNT'. {valueReference.reference.resolve().code.coding.code = 'PROV' or valueReference.reference.resolve().code.coding.code = 'AGNT'}</t>
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}comp-3:La valeur du PractitionerRole.code dans l'extension[party]' doit être 'PROV' ou 'AGNT'. {value.resolve().code.coding.code.contains('PROV') or value.resolve().code.coding.code.contains('AGNT')}</t>
   </si>
   <si>
     <t>Composition.extension:participant.extension:party.id</t>
@@ -2355,7 +2355,7 @@
     <t>translation</t>
   </si>
   <si>
-    <t>translation : obligatoire pour : un CR d’imagerie et un CR d’examen de l’enfant</t>
+    <t>translation : un ensemble d’équivalents de l'élément 'code' dans d’autres terminologies</t>
   </si>
   <si>
     <t>Composition.event.period</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-composition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-25T13:52:25+00:00</t>
+    <t>2025-03-25T14:07:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-composition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-25T14:07:20+00:00</t>
+    <t>2025-03-31T09:17:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-composition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T09:17:15+00:00</t>
+    <t>2025-04-14T15:21:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -265,10 +265,10 @@
 </t>
   </si>
   <si>
-    <t>Clinical document</t>
-  </si>
-  <si>
-    <t>Clinical document.</t>
+    <t>A set of resources composed into a single coherent clinical statement with clinical attestation</t>
+  </si>
+  <si>
+    <t>A set of healthcare-related information that is assembled together into a single logical package that provides a single coherent statement of meaning, establishes its own context and that has clinical attestation with regard to who is making the statement. A Composition defines the structure and narrative content necessary for a document. However, a Composition alone does not constitute a document. Rather, the Composition must be the first entry in a Bundle where Bundle.type=document, and any other resources referenced from Composition must be included as subsequent entries in the Bundle (for example Patient, Practitioner, Encounter, etc.).</t>
   </si>
   <si>
     <t>While the focus of this specification is on patient-specific clinical statements, this resource can also apply to other healthcare-related statements such as study protocol designs, healthcare invoices and other activities that are not necessarily patient-specific or clinical.</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-composition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-14T15:21:44+00:00</t>
+    <t>2025-04-23T09:31:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -980,7 +980,7 @@
     <t>Composition.extension:informant.extension:party.value[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-practitionerRole-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-related-person-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-patient-fhir-document)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-practitionerRole-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-related-person-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-patient-ins-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-patient-document)
 </t>
   </si>
   <si>
@@ -1400,7 +1400,7 @@
     <t>Composition.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-patient-fhir-document)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-patient-ins-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-patient-document)
 </t>
   </si>
   <si>
@@ -1579,7 +1579,7 @@
     <t>Composition.author</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-practitionerRole-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-patient-fhir-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-device-document)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-practitionerRole-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-patient-ins-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-patient-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-device-document)
 </t>
   </si>
   <si>
@@ -2718,15 +2718,15 @@
   <dimension ref="A1:AO222"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="78.42578125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="41.15234375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="22.97265625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="97.09375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="67.234375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="35.28125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="19.6953125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="83.23828125" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2737,27 +2737,27 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="38.2265625" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="98.61328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="96.21484375" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="34.859375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="32.7734375" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="82.484375" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="42.39453125" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="73.69140625" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="36.34765625" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="63.17578125" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="31.65234375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>91</v>

--- a/htr-FHIR/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-composition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-23T09:31:53+00:00</t>
+    <t>2025-04-24T14:52:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-composition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-24T14:52:25+00:00</t>
+    <t>2025-04-28T07:47:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-composition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T07:47:42+00:00</t>
+    <t>2025-04-28T07:48:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-composition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T07:48:19+00:00</t>
+    <t>2025-04-28T09:06:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-composition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T09:06:14+00:00</t>
+    <t>2025-04-28T09:53:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-composition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T09:53:39+00:00</t>
+    <t>2025-05-06T15:44:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-composition-document.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$222</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$229</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8196" uniqueCount="768">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8449" uniqueCount="777">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-06T15:44:46+00:00</t>
+    <t>2025-05-06T15:53:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2293,10 +2293,6 @@
     <t>Provides context for the composition and creates a linkage between a resource describing an event and the composition created describing the event.</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-comp-2:L'exécutant de l’évènement et la date et heure de l’évènement sont obligatoires dans l'acte principal. {detail.exists() implies period.exists()}</t>
-  </si>
-  <si>
     <t>outboundRelationship[typeCode="SUBJ"].target[classCode&lt;'ACT']</t>
   </si>
   <si>
@@ -2312,6 +2308,22 @@
     <t>Composition.event.extension</t>
   </si>
   <si>
+    <t>Composition.event.extension:perfomer</t>
+  </si>
+  <si>
+    <t>perfomer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-performer-event}
+</t>
+  </si>
+  <si>
+    <t>Exécutant de l’évènement documenté</t>
+  </si>
+  <si>
+    <t>Extension permettant d'ajouter un perfomer à l'élément event d'une Composition.</t>
+  </si>
+  <si>
     <t>Composition.event.modifierExtension</t>
   </si>
   <si>
@@ -2333,46 +2345,28 @@
     <t>http://terminology.hl7.org/ValueSet/v3-ActCode</t>
   </si>
   <si>
-    <t xml:space="preserve">value:coding.code}
+    <t>DocumentReference.event.code</t>
+  </si>
+  <si>
+    <t>Composition.event.period</t>
+  </si>
+  <si>
+    <t>Date et heure de l’évènement documenté</t>
+  </si>
+  <si>
+    <t>The period of time covered by the documentation. There is no assertion that the documentation is a complete representation for this period, only that it documents events during this time.</t>
+  </si>
+  <si>
+    <t>DocumentReference.event.period</t>
+  </si>
+  <si>
+    <t>Composition.event.detail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Resource)
 </t>
   </si>
   <si>
-    <t>DocumentReference.event.code</t>
-  </si>
-  <si>
-    <t>Composition.event.code:codeEvenement</t>
-  </si>
-  <si>
-    <t>codeEvenement</t>
-  </si>
-  <si>
-    <t>Code de l’évènement documenté</t>
-  </si>
-  <si>
-    <t>Composition.event.code:translation</t>
-  </si>
-  <si>
-    <t>translation</t>
-  </si>
-  <si>
-    <t>translation : un ensemble d’équivalents de l'élément 'code' dans d’autres terminologies</t>
-  </si>
-  <si>
-    <t>Composition.event.period</t>
-  </si>
-  <si>
-    <t>Date et heure de l’évènement documenté</t>
-  </si>
-  <si>
-    <t>The period of time covered by the documentation. There is no assertion that the documentation is a complete representation for this period, only that it documents events during this time.</t>
-  </si>
-  <si>
-    <t>DocumentReference.event.period</t>
-  </si>
-  <si>
-    <t>Composition.event.detail</t>
-  </si>
-  <si>
     <t>The event(s) being documented</t>
   </si>
   <si>
@@ -2380,6 +2374,39 @@
   </si>
   <si>
     <t>.outboundRelationship[typeCode="SUBJ"].target</t>
+  </si>
+  <si>
+    <t>Composition.event:principalEvent</t>
+  </si>
+  <si>
+    <t>principalEvent</t>
+  </si>
+  <si>
+    <t>Evènement documenté principal</t>
+  </si>
+  <si>
+    <t>Composition.event:principalEvent.id</t>
+  </si>
+  <si>
+    <t>Composition.event:principalEvent.extension</t>
+  </si>
+  <si>
+    <t>Composition.event:principalEvent.extension:perfomer</t>
+  </si>
+  <si>
+    <t>Exécutant de l'évènement documenté principal</t>
+  </si>
+  <si>
+    <t>Composition.event:principalEvent.modifierExtension</t>
+  </si>
+  <si>
+    <t>Composition.event:principalEvent.code</t>
+  </si>
+  <si>
+    <t>Composition.event:principalEvent.period</t>
+  </si>
+  <si>
+    <t>Composition.event:principalEvent.detail</t>
   </si>
   <si>
     <t>Composition.section</t>
@@ -2715,7 +2742,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO222"/>
+  <dimension ref="A1:AO229"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="67.234375" customWidth="true" bestFit="true"/>
@@ -27535,16 +27562,14 @@
         <v>78</v>
       </c>
       <c r="AB213" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC213" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="AC213" s="2"/>
       <c r="AD213" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE213" t="s" s="2">
-        <v>78</v>
+        <v>118</v>
       </c>
       <c r="AF213" t="s" s="2">
         <v>728</v>
@@ -27559,19 +27584,19 @@
         <v>78</v>
       </c>
       <c r="AJ213" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK213" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL213" t="s" s="2">
         <v>733</v>
       </c>
-      <c r="AK213" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL213" t="s" s="2">
+      <c r="AM213" t="s" s="2">
         <v>734</v>
       </c>
-      <c r="AM213" t="s" s="2">
+      <c r="AN213" t="s" s="2">
         <v>735</v>
-      </c>
-      <c r="AN213" t="s" s="2">
-        <v>736</v>
       </c>
       <c r="AO213" t="s" s="2">
         <v>78</v>
@@ -27579,10 +27604,10 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -27694,14 +27719,14 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
-        <v>111</v>
+        <v>78</v>
       </c>
       <c r="E215" s="2"/>
       <c r="F215" t="s" s="2">
@@ -27723,14 +27748,12 @@
         <v>112</v>
       </c>
       <c r="L215" t="s" s="2">
-        <v>113</v>
+        <v>197</v>
       </c>
       <c r="M215" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N215" t="s" s="2">
-        <v>115</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="N215" s="2"/>
       <c r="O215" s="2"/>
       <c r="P215" t="s" s="2">
         <v>78</v>
@@ -27767,16 +27790,14 @@
         <v>78</v>
       </c>
       <c r="AB215" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC215" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="AC215" s="2"/>
       <c r="AD215" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE215" t="s" s="2">
-        <v>78</v>
+        <v>118</v>
       </c>
       <c r="AF215" t="s" s="2">
         <v>119</v>
@@ -27797,7 +27818,7 @@
         <v>78</v>
       </c>
       <c r="AL215" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="AM215" t="s" s="2">
         <v>78</v>
@@ -27811,46 +27832,44 @@
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
+        <v>738</v>
+      </c>
+      <c r="B216" t="s" s="2">
+        <v>737</v>
+      </c>
+      <c r="C216" t="s" s="2">
         <v>739</v>
       </c>
-      <c r="B216" t="s" s="2">
-        <v>739</v>
-      </c>
-      <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
-        <v>547</v>
+        <v>78</v>
       </c>
       <c r="E216" s="2"/>
       <c r="F216" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G216" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H216" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I216" t="s" s="2">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="J216" t="s" s="2">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="K216" t="s" s="2">
-        <v>112</v>
+        <v>740</v>
       </c>
       <c r="L216" t="s" s="2">
-        <v>548</v>
+        <v>741</v>
       </c>
       <c r="M216" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="N216" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O216" t="s" s="2">
-        <v>550</v>
-      </c>
+        <v>742</v>
+      </c>
+      <c r="N216" s="2"/>
+      <c r="O216" s="2"/>
       <c r="P216" t="s" s="2">
         <v>78</v>
       </c>
@@ -27898,7 +27917,7 @@
         <v>78</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>551</v>
+        <v>119</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>79</v>
@@ -27907,7 +27926,7 @@
         <v>80</v>
       </c>
       <c r="AI216" t="s" s="2">
-        <v>78</v>
+        <v>205</v>
       </c>
       <c r="AJ216" t="s" s="2">
         <v>120</v>
@@ -27916,7 +27935,7 @@
         <v>78</v>
       </c>
       <c r="AL216" t="s" s="2">
-        <v>195</v>
+        <v>78</v>
       </c>
       <c r="AM216" t="s" s="2">
         <v>78</v>
@@ -27930,14 +27949,14 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
-        <v>78</v>
+        <v>547</v>
       </c>
       <c r="E217" s="2"/>
       <c r="F217" t="s" s="2">
@@ -27950,24 +27969,26 @@
         <v>78</v>
       </c>
       <c r="I217" t="s" s="2">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="J217" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K217" t="s" s="2">
-        <v>233</v>
+        <v>112</v>
       </c>
       <c r="L217" t="s" s="2">
-        <v>741</v>
+        <v>548</v>
       </c>
       <c r="M217" t="s" s="2">
-        <v>742</v>
+        <v>549</v>
       </c>
       <c r="N217" t="s" s="2">
-        <v>743</v>
-      </c>
-      <c r="O217" s="2"/>
+        <v>115</v>
+      </c>
+      <c r="O217" t="s" s="2">
+        <v>550</v>
+      </c>
       <c r="P217" t="s" s="2">
         <v>78</v>
       </c>
@@ -27991,29 +28012,31 @@
         <v>78</v>
       </c>
       <c r="X217" t="s" s="2">
-        <v>161</v>
+        <v>78</v>
       </c>
       <c r="Y217" t="s" s="2">
-        <v>744</v>
+        <v>78</v>
       </c>
       <c r="Z217" t="s" s="2">
-        <v>745</v>
+        <v>78</v>
       </c>
       <c r="AA217" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB217" t="s" s="2">
-        <v>746</v>
-      </c>
-      <c r="AC217" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC217" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD217" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE217" t="s" s="2">
-        <v>118</v>
+        <v>78</v>
       </c>
       <c r="AF217" t="s" s="2">
-        <v>740</v>
+        <v>551</v>
       </c>
       <c r="AG217" t="s" s="2">
         <v>79</v>
@@ -28025,19 +28048,19 @@
         <v>78</v>
       </c>
       <c r="AJ217" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK217" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL217" t="s" s="2">
-        <v>428</v>
+        <v>195</v>
       </c>
       <c r="AM217" t="s" s="2">
-        <v>428</v>
+        <v>78</v>
       </c>
       <c r="AN217" t="s" s="2">
-        <v>747</v>
+        <v>78</v>
       </c>
       <c r="AO217" t="s" s="2">
         <v>78</v>
@@ -28045,14 +28068,12 @@
     </row>
     <row r="218" hidden="true">
       <c r="A218" t="s" s="2">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>740</v>
-      </c>
-      <c r="C218" t="s" s="2">
-        <v>749</v>
-      </c>
+        <v>744</v>
+      </c>
+      <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
         <v>78</v>
       </c>
@@ -28061,7 +28082,7 @@
         <v>79</v>
       </c>
       <c r="G218" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H218" t="s" s="2">
         <v>78</v>
@@ -28076,13 +28097,13 @@
         <v>233</v>
       </c>
       <c r="L218" t="s" s="2">
-        <v>750</v>
+        <v>745</v>
       </c>
       <c r="M218" t="s" s="2">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="N218" t="s" s="2">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="O218" s="2"/>
       <c r="P218" t="s" s="2">
@@ -28111,28 +28132,28 @@
         <v>161</v>
       </c>
       <c r="Y218" t="s" s="2">
+        <v>748</v>
+      </c>
+      <c r="Z218" t="s" s="2">
+        <v>749</v>
+      </c>
+      <c r="AA218" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB218" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC218" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD218" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE218" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF218" t="s" s="2">
         <v>744</v>
-      </c>
-      <c r="Z218" t="s" s="2">
-        <v>745</v>
-      </c>
-      <c r="AA218" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB218" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC218" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD218" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE218" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF218" t="s" s="2">
-        <v>740</v>
       </c>
       <c r="AG218" t="s" s="2">
         <v>79</v>
@@ -28156,7 +28177,7 @@
         <v>428</v>
       </c>
       <c r="AN218" t="s" s="2">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="AO218" t="s" s="2">
         <v>78</v>
@@ -28167,11 +28188,9 @@
         <v>751</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>740</v>
-      </c>
-      <c r="C219" t="s" s="2">
-        <v>752</v>
-      </c>
+        <v>751</v>
+      </c>
+      <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
         <v>78</v>
       </c>
@@ -28180,7 +28199,7 @@
         <v>79</v>
       </c>
       <c r="G219" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H219" t="s" s="2">
         <v>78</v>
@@ -28192,17 +28211,15 @@
         <v>92</v>
       </c>
       <c r="K219" t="s" s="2">
-        <v>233</v>
+        <v>257</v>
       </c>
       <c r="L219" t="s" s="2">
+        <v>752</v>
+      </c>
+      <c r="M219" t="s" s="2">
         <v>753</v>
       </c>
-      <c r="M219" t="s" s="2">
-        <v>742</v>
-      </c>
-      <c r="N219" t="s" s="2">
-        <v>743</v>
-      </c>
+      <c r="N219" s="2"/>
       <c r="O219" s="2"/>
       <c r="P219" t="s" s="2">
         <v>78</v>
@@ -28227,13 +28244,13 @@
         <v>78</v>
       </c>
       <c r="X219" t="s" s="2">
-        <v>161</v>
+        <v>78</v>
       </c>
       <c r="Y219" t="s" s="2">
-        <v>744</v>
+        <v>78</v>
       </c>
       <c r="Z219" t="s" s="2">
-        <v>745</v>
+        <v>78</v>
       </c>
       <c r="AA219" t="s" s="2">
         <v>78</v>
@@ -28251,13 +28268,13 @@
         <v>78</v>
       </c>
       <c r="AF219" t="s" s="2">
-        <v>740</v>
+        <v>751</v>
       </c>
       <c r="AG219" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH219" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI219" t="s" s="2">
         <v>78</v>
@@ -28269,13 +28286,13 @@
         <v>78</v>
       </c>
       <c r="AL219" t="s" s="2">
-        <v>428</v>
+        <v>495</v>
       </c>
       <c r="AM219" t="s" s="2">
-        <v>428</v>
+        <v>495</v>
       </c>
       <c r="AN219" t="s" s="2">
-        <v>747</v>
+        <v>754</v>
       </c>
       <c r="AO219" t="s" s="2">
         <v>78</v>
@@ -28283,10 +28300,10 @@
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -28309,13 +28326,13 @@
         <v>92</v>
       </c>
       <c r="K220" t="s" s="2">
-        <v>257</v>
+        <v>756</v>
       </c>
       <c r="L220" t="s" s="2">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="M220" t="s" s="2">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="N220" s="2"/>
       <c r="O220" s="2"/>
@@ -28366,13 +28383,13 @@
         <v>78</v>
       </c>
       <c r="AF220" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="AG220" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH220" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI220" t="s" s="2">
         <v>78</v>
@@ -28384,13 +28401,13 @@
         <v>78</v>
       </c>
       <c r="AL220" t="s" s="2">
-        <v>495</v>
+        <v>759</v>
       </c>
       <c r="AM220" t="s" s="2">
-        <v>495</v>
+        <v>109</v>
       </c>
       <c r="AN220" t="s" s="2">
-        <v>757</v>
+        <v>78</v>
       </c>
       <c r="AO220" t="s" s="2">
         <v>78</v>
@@ -28398,18 +28415,20 @@
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>758</v>
-      </c>
-      <c r="C221" s="2"/>
+        <v>728</v>
+      </c>
+      <c r="C221" t="s" s="2">
+        <v>761</v>
+      </c>
       <c r="D221" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E221" s="2"/>
       <c r="F221" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="G221" t="s" s="2">
         <v>91</v>
@@ -28424,16 +28443,20 @@
         <v>92</v>
       </c>
       <c r="K221" t="s" s="2">
-        <v>265</v>
+        <v>534</v>
       </c>
       <c r="L221" t="s" s="2">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="M221" t="s" s="2">
-        <v>760</v>
-      </c>
-      <c r="N221" s="2"/>
-      <c r="O221" s="2"/>
+        <v>730</v>
+      </c>
+      <c r="N221" t="s" s="2">
+        <v>731</v>
+      </c>
+      <c r="O221" t="s" s="2">
+        <v>732</v>
+      </c>
       <c r="P221" t="s" s="2">
         <v>78</v>
       </c>
@@ -28481,7 +28504,7 @@
         <v>78</v>
       </c>
       <c r="AF221" t="s" s="2">
-        <v>758</v>
+        <v>728</v>
       </c>
       <c r="AG221" t="s" s="2">
         <v>79</v>
@@ -28499,13 +28522,13 @@
         <v>78</v>
       </c>
       <c r="AL221" t="s" s="2">
-        <v>761</v>
+        <v>733</v>
       </c>
       <c r="AM221" t="s" s="2">
-        <v>109</v>
+        <v>734</v>
       </c>
       <c r="AN221" t="s" s="2">
-        <v>78</v>
+        <v>735</v>
       </c>
       <c r="AO221" t="s" s="2">
         <v>78</v>
@@ -28513,10 +28536,10 @@
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>762</v>
+        <v>736</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -28524,13 +28547,13 @@
       </c>
       <c r="E222" s="2"/>
       <c r="F222" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="G222" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H222" t="s" s="2">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="I222" t="s" s="2">
         <v>78</v>
@@ -28539,13 +28562,13 @@
         <v>78</v>
       </c>
       <c r="K222" t="s" s="2">
-        <v>534</v>
+        <v>105</v>
       </c>
       <c r="L222" t="s" s="2">
-        <v>763</v>
+        <v>106</v>
       </c>
       <c r="M222" t="s" s="2">
-        <v>764</v>
+        <v>107</v>
       </c>
       <c r="N222" s="2"/>
       <c r="O222" s="2"/>
@@ -28584,48 +28607,859 @@
         <v>78</v>
       </c>
       <c r="AB222" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC222" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD222" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE222" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF222" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AG222" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH222" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI222" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ222" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK222" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL222" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AM222" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN222" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO222" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="223" hidden="true">
+      <c r="A223" t="s" s="2">
+        <v>764</v>
+      </c>
+      <c r="B223" t="s" s="2">
+        <v>737</v>
+      </c>
+      <c r="C223" s="2"/>
+      <c r="D223" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E223" s="2"/>
+      <c r="F223" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="G223" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H223" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I223" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J223" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K223" t="s" s="2">
+        <v>740</v>
+      </c>
+      <c r="L223" t="s" s="2">
+        <v>741</v>
+      </c>
+      <c r="M223" t="s" s="2">
+        <v>742</v>
+      </c>
+      <c r="N223" s="2"/>
+      <c r="O223" s="2"/>
+      <c r="P223" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q223" s="2"/>
+      <c r="R223" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S223" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T223" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U223" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V223" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W223" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X223" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y223" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z223" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA223" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB223" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AC223" s="2"/>
+      <c r="AD223" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE223" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AF223" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AG223" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH223" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI223" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ223" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AK223" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL223" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM223" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN223" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO223" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="224" hidden="true">
+      <c r="A224" t="s" s="2">
+        <v>765</v>
+      </c>
+      <c r="B224" t="s" s="2">
+        <v>737</v>
+      </c>
+      <c r="C224" t="s" s="2">
+        <v>739</v>
+      </c>
+      <c r="D224" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E224" s="2"/>
+      <c r="F224" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="G224" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H224" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I224" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J224" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K224" t="s" s="2">
+        <v>740</v>
+      </c>
+      <c r="L224" t="s" s="2">
+        <v>766</v>
+      </c>
+      <c r="M224" t="s" s="2">
+        <v>742</v>
+      </c>
+      <c r="N224" s="2"/>
+      <c r="O224" s="2"/>
+      <c r="P224" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q224" s="2"/>
+      <c r="R224" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S224" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T224" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U224" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V224" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W224" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X224" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y224" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z224" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA224" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB224" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC224" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD224" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE224" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF224" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AG224" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH224" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI224" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="AJ224" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AK224" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL224" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM224" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN224" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO224" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="225" hidden="true">
+      <c r="A225" t="s" s="2">
+        <v>767</v>
+      </c>
+      <c r="B225" t="s" s="2">
+        <v>743</v>
+      </c>
+      <c r="C225" s="2"/>
+      <c r="D225" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="E225" s="2"/>
+      <c r="F225" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G225" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H225" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I225" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="J225" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K225" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L225" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="M225" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="N225" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="O225" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="P225" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q225" s="2"/>
+      <c r="R225" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S225" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T225" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U225" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V225" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W225" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X225" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y225" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z225" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA225" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB225" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC225" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD225" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE225" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF225" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="AG225" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH225" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI225" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ225" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AK225" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL225" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="AM225" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN225" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO225" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="226" hidden="true">
+      <c r="A226" t="s" s="2">
+        <v>768</v>
+      </c>
+      <c r="B226" t="s" s="2">
+        <v>744</v>
+      </c>
+      <c r="C226" s="2"/>
+      <c r="D226" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E226" s="2"/>
+      <c r="F226" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G226" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H226" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I226" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J226" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K226" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="L226" t="s" s="2">
+        <v>745</v>
+      </c>
+      <c r="M226" t="s" s="2">
+        <v>746</v>
+      </c>
+      <c r="N226" t="s" s="2">
+        <v>747</v>
+      </c>
+      <c r="O226" s="2"/>
+      <c r="P226" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q226" s="2"/>
+      <c r="R226" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S226" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T226" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U226" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V226" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W226" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X226" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="Y226" t="s" s="2">
+        <v>748</v>
+      </c>
+      <c r="Z226" t="s" s="2">
+        <v>749</v>
+      </c>
+      <c r="AA226" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB226" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC226" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD226" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE226" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF226" t="s" s="2">
+        <v>744</v>
+      </c>
+      <c r="AG226" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH226" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI226" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ226" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK226" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL226" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AM226" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AN226" t="s" s="2">
+        <v>750</v>
+      </c>
+      <c r="AO226" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="227" hidden="true">
+      <c r="A227" t="s" s="2">
+        <v>769</v>
+      </c>
+      <c r="B227" t="s" s="2">
+        <v>751</v>
+      </c>
+      <c r="C227" s="2"/>
+      <c r="D227" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E227" s="2"/>
+      <c r="F227" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="G227" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H227" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I227" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J227" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K227" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="L227" t="s" s="2">
+        <v>752</v>
+      </c>
+      <c r="M227" t="s" s="2">
+        <v>753</v>
+      </c>
+      <c r="N227" s="2"/>
+      <c r="O227" s="2"/>
+      <c r="P227" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q227" s="2"/>
+      <c r="R227" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S227" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T227" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U227" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V227" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W227" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X227" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y227" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z227" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA227" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB227" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC227" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD227" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE227" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF227" t="s" s="2">
+        <v>751</v>
+      </c>
+      <c r="AG227" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH227" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI227" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ227" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK227" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL227" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="AM227" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="AN227" t="s" s="2">
+        <v>754</v>
+      </c>
+      <c r="AO227" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="228" hidden="true">
+      <c r="A228" t="s" s="2">
+        <v>770</v>
+      </c>
+      <c r="B228" t="s" s="2">
+        <v>755</v>
+      </c>
+      <c r="C228" s="2"/>
+      <c r="D228" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E228" s="2"/>
+      <c r="F228" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G228" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H228" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I228" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J228" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K228" t="s" s="2">
+        <v>756</v>
+      </c>
+      <c r="L228" t="s" s="2">
+        <v>757</v>
+      </c>
+      <c r="M228" t="s" s="2">
+        <v>758</v>
+      </c>
+      <c r="N228" s="2"/>
+      <c r="O228" s="2"/>
+      <c r="P228" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q228" s="2"/>
+      <c r="R228" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S228" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T228" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U228" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V228" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W228" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X228" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y228" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z228" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA228" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB228" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC228" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD228" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE228" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF228" t="s" s="2">
+        <v>755</v>
+      </c>
+      <c r="AG228" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH228" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI228" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ228" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK228" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL228" t="s" s="2">
+        <v>759</v>
+      </c>
+      <c r="AM228" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AN228" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO228" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="229" hidden="true">
+      <c r="A229" t="s" s="2">
+        <v>771</v>
+      </c>
+      <c r="B229" t="s" s="2">
+        <v>771</v>
+      </c>
+      <c r="C229" s="2"/>
+      <c r="D229" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E229" s="2"/>
+      <c r="F229" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="G229" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H229" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="I229" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J229" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K229" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="L229" t="s" s="2">
+        <v>772</v>
+      </c>
+      <c r="M229" t="s" s="2">
+        <v>773</v>
+      </c>
+      <c r="N229" s="2"/>
+      <c r="O229" s="2"/>
+      <c r="P229" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q229" s="2"/>
+      <c r="R229" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S229" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T229" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U229" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V229" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W229" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X229" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y229" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z229" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA229" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB229" t="s" s="2">
         <v>609</v>
       </c>
-      <c r="AC222" s="2"/>
-      <c r="AD222" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE222" t="s" s="2">
+      <c r="AC229" s="2"/>
+      <c r="AD229" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE229" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="AF222" t="s" s="2">
-        <v>762</v>
-      </c>
-      <c r="AG222" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH222" t="s" s="2">
+      <c r="AF229" t="s" s="2">
+        <v>771</v>
+      </c>
+      <c r="AG229" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH229" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="AI222" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ222" t="s" s="2">
-        <v>765</v>
-      </c>
-      <c r="AK222" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL222" t="s" s="2">
-        <v>766</v>
-      </c>
-      <c r="AM222" t="s" s="2">
-        <v>767</v>
-      </c>
-      <c r="AN222" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO222" t="s" s="2">
+      <c r="AI229" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ229" t="s" s="2">
+        <v>774</v>
+      </c>
+      <c r="AK229" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL229" t="s" s="2">
+        <v>775</v>
+      </c>
+      <c r="AM229" t="s" s="2">
+        <v>776</v>
+      </c>
+      <c r="AN229" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO229" t="s" s="2">
         <v>78</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO222">
+  <autoFilter ref="A1:AO229">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -28635,7 +29469,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI221">
+  <conditionalFormatting sqref="A2:AI228">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/htr-FHIR/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-composition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-06T15:53:54+00:00</t>
+    <t>2025-05-06T15:58:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-composition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-06T15:58:22+00:00</t>
+    <t>2025-05-20T10:20:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-composition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T10:20:09+00:00</t>
+    <t>2025-05-20T12:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
